--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA068F43-31CF-44BF-B739-F9E33A3CA8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3CB6B0-9083-4D22-A5DA-677685057DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -331,7 +331,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -339,11 +339,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -352,11 +361,66 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="9">
+    <dxf>
+      <border>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <top/>
@@ -27692,7 +27756,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B72" si="0">IF(A7=A8, B7+1, 1)</f>
+        <f t="shared" ref="B8:B73" si="0">IF(A7=A8, B7+1, 1)</f>
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -27979,7 +28043,7 @@
         <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2">
         <f>IF(IF(RIGHT($A20,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A20,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28103,21 +28167,21 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D26" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C26), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2">
         <f>IF(IF(RIGHT($A26,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A26,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28126,21 +28190,21 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D27" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C27), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F27" s="2">
         <f>IF(IF(RIGHT($A27,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A27,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28153,17 +28217,17 @@
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D28" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C28), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" s="2">
         <f>IF(IF(RIGHT($A28,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A28,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28176,21 +28240,21 @@
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D29" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C29), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F29" s="2">
         <f>IF(IF(RIGHT($A29,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A29,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -28199,14 +28263,14 @@
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D30" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C30), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E30">
         <v>4</v>
@@ -28222,21 +28286,21 @@
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D31" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C31), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
       </c>
       <c r="E31">
         <v>4</v>
       </c>
       <c r="F31" s="2">
         <f>IF(IF(RIGHT($A31,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A31,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -28245,21 +28309,21 @@
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D32" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C32), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E32">
         <v>4</v>
       </c>
       <c r="F32" s="2">
         <f>IF(IF(RIGHT($A32,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A32,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -28268,14 +28332,14 @@
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D33" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C33), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E33">
         <v>4</v>
@@ -28291,21 +28355,21 @@
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D34" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C34), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E34">
         <v>4</v>
       </c>
       <c r="F34" s="2">
         <f>IF(IF(RIGHT($A34,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A34,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -28314,21 +28378,21 @@
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D35" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C35), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35" s="2">
         <f>IF(IF(RIGHT($A35,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A35,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -28337,21 +28401,21 @@
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D36" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C36), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Sparkle Pen, 5Pck</v>
+        <v>Scented Marker 10 Colors</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F36" s="2">
         <f>IF(IF(RIGHT($A36,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A36,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -28360,21 +28424,21 @@
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D37" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C37), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Swirl Pen, 5Pck</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2">
         <f>IF(IF(RIGHT($A37,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A37,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -28383,60 +28447,60 @@
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D38" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C38), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Stacking Highlighters - 2-pack</v>
+        <v>Scented Sparkle Pen, 5Pck</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="2">
         <f>IF(IF(RIGHT($A38,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A38,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D39" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C39), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>Scented Swirl Pen, 5Pck</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="2">
         <f>IF(IF(RIGHT($A39,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A39,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D40" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C40), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>Scented Stacking Highlighters - 2-pack</v>
       </c>
       <c r="E40">
         <v>4</v>
@@ -28452,7 +28516,7 @@
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>37</v>
@@ -28475,7 +28539,7 @@
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -28498,7 +28562,7 @@
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>19</v>
@@ -28521,7 +28585,7 @@
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>33</v>
@@ -28544,7 +28608,7 @@
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>34</v>
@@ -28567,7 +28631,7 @@
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>52</v>
@@ -28590,7 +28654,7 @@
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>55</v>
@@ -28613,7 +28677,7 @@
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>23</v>
@@ -28636,17 +28700,17 @@
       </c>
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D49" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C49), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" s="2">
         <f>IF(IF(RIGHT($A49,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A49,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28659,17 +28723,17 @@
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="D50" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C50), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E50">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F50" s="2">
         <f>IF(IF(RIGHT($A50,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A50,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28682,17 +28746,17 @@
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D51" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51" s="2">
         <f>IF(IF(RIGHT($A51,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A51,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28705,14 +28769,14 @@
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="D52" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E52">
         <v>4</v>
@@ -28722,25 +28786,25 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53">
+    <row r="53" spans="1:6" s="6" customFormat="1">
+      <c r="A53" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="6">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" t="str">
+        <v>13</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E53">
-        <v>8</v>
-      </c>
-      <c r="F53" s="2">
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+      </c>
+      <c r="E53" s="6">
+        <v>4</v>
+      </c>
+      <c r="F53" s="8">
         <f>IF(IF(RIGHT($A53,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A53,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
@@ -28751,14 +28815,14 @@
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D54" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C54), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E54">
         <v>8</v>
@@ -28774,17 +28838,17 @@
       </c>
       <c r="B55">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D55" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C55), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F55" s="2">
         <f>IF(IF(RIGHT($A55,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A55,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28797,14 +28861,14 @@
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="D56" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E56">
         <v>4</v>
@@ -28820,14 +28884,14 @@
       </c>
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="D57" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C57), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E57">
         <v>4</v>
@@ -28843,17 +28907,17 @@
       </c>
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D58" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F58" s="2">
         <f>IF(IF(RIGHT($A58,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A58,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28866,14 +28930,14 @@
       </c>
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D59" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E59">
         <v>8</v>
@@ -28889,17 +28953,17 @@
       </c>
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D60" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E60">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F60" s="2">
         <f>IF(IF(RIGHT($A60,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A60,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -28912,14 +28976,14 @@
       </c>
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D61" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E61">
         <v>4</v>
@@ -28935,14 +28999,14 @@
       </c>
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D62" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E62">
         <v>4</v>
@@ -28958,14 +29022,14 @@
       </c>
       <c r="B63">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D63" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E63">
         <v>4</v>
@@ -28977,25 +29041,25 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E64">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F64" s="2">
         <f>IF(IF(RIGHT($A64,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A64,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -29004,21 +29068,21 @@
       </c>
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D65" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
       </c>
       <c r="E65">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F65" s="2">
         <f>IF(IF(RIGHT($A65,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A65,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -29027,17 +29091,17 @@
       </c>
       <c r="B66">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E66">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F66" s="2">
         <f>IF(IF(RIGHT($A66,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A66,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29050,17 +29114,17 @@
       </c>
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F67" s="2">
         <f>IF(IF(RIGHT($A67,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A67,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29073,14 +29137,14 @@
       </c>
       <c r="B68">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E68">
         <v>12</v>
@@ -29096,14 +29160,14 @@
       </c>
       <c r="B69">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="D69" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E69">
         <v>4</v>
@@ -29119,17 +29183,17 @@
       </c>
       <c r="B70">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F70" s="2">
         <f>IF(IF(RIGHT($A70,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A70,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29142,17 +29206,17 @@
       </c>
       <c r="B71">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D71" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E71">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F71" s="2">
         <f>IF(IF(RIGHT($A71,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A71,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29165,21 +29229,21 @@
       </c>
       <c r="B72">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D72" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F72" s="2">
         <f>IF(IF(RIGHT($A72,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A72,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -29187,15 +29251,15 @@
         <v>51</v>
       </c>
       <c r="B73">
-        <f t="shared" ref="B73:B136" si="1">IF(A72=A73, B72+1, 1)</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="D73" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E73">
         <v>12</v>
@@ -29210,15 +29274,15 @@
         <v>51</v>
       </c>
       <c r="B74">
-        <f t="shared" si="1"/>
-        <v>11</v>
+        <f t="shared" ref="B74:B137" si="1">IF(A73=A74, B73+1, 1)</f>
+        <v>10</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E74">
         <v>12</v>
@@ -29234,7 +29298,7 @@
       </c>
       <c r="B75">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>79</v>
@@ -29257,7 +29321,7 @@
       </c>
       <c r="B76">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>62</v>
@@ -29280,7 +29344,7 @@
       </c>
       <c r="B77">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>27</v>
@@ -29303,7 +29367,7 @@
       </c>
       <c r="B78">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>76</v>
@@ -29326,7 +29390,7 @@
       </c>
       <c r="B79">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>26</v>
@@ -29349,7 +29413,7 @@
       </c>
       <c r="B80">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>25</v>
@@ -29359,7 +29423,7 @@
         <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F80" s="2">
         <f>IF(IF(RIGHT($A80,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A80,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29372,7 +29436,7 @@
       </c>
       <c r="B81">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>24</v>
@@ -29382,7 +29446,7 @@
         <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E81">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F81" s="2">
         <f>IF(IF(RIGHT($A81,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A81,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30659,7 +30723,7 @@
         <v>80</v>
       </c>
       <c r="B137">
-        <f t="shared" ref="B137:B144" si="2">IF(A136=A137, B136+1, 1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="C137" s="1" t="s">
@@ -30682,7 +30746,7 @@
         <v>80</v>
       </c>
       <c r="B138">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="B138:B144" si="2">IF(A137=A138, B137+1, 1)</f>
         <v>16</v>
       </c>
       <c r="C138" s="1" t="s">
@@ -30843,24 +30907,49 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:XFD10">
-    <cfRule type="expression" dxfId="3" priority="2">
+  <conditionalFormatting sqref="A5:XFD10 A12:XFD21 A25:XFD39 A42:XFD42 A44:XFD52 A54:XFD63 A66:XFD72 A74:XFD79 A81:XFD126">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>IF($A5&lt;&gt;$A6, TRUE, FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11:XFD11">
-    <cfRule type="expression" dxfId="2" priority="7">
+  <conditionalFormatting sqref="A11:XFD11 A40:XFD40 A64:XFD64">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>IF($A11&lt;&gt;$A13, TRUE, FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:XFD126">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>IF($A12&lt;&gt;$A13, TRUE, FALSE)</formula>
+  <conditionalFormatting sqref="D127:F144">
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>IF($A127&lt;&gt;$A128, TRUE, FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D127:F144">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>IF($A127&lt;&gt;$A128, TRUE, FALSE)</formula>
+  <conditionalFormatting sqref="A22:XFD22 A41:XFD41">
+    <cfRule type="expression" dxfId="5" priority="11">
+      <formula>IF($A22&lt;&gt;$A25, TRUE, FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:XFD24">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>IF($A23&lt;&gt;$A24, TRUE, FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43:XFD43">
+    <cfRule type="expression" dxfId="3" priority="14">
+      <formula>IF($A43&lt;&gt;$A41, TRUE, FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53:XFD53 A80:XFD80">
+    <cfRule type="expression" dxfId="2" priority="17">
+      <formula>IF($A53&lt;&gt;#REF!, TRUE, FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A73:XFD73">
+    <cfRule type="expression" dxfId="1" priority="20">
+      <formula>IF($A73&lt;&gt;$A65, TRUE, FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65:XFD65">
+    <cfRule type="expression" dxfId="0" priority="21">
+      <formula>IF($A65&lt;&gt;$A74, TRUE, FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30868,26 +30957,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B10405EB6D76C04A99D739F71CB1C882" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="588855ac044783769b53e0cfeb370d1a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="856a7437-a7e7-4452-817c-46e435f59c4c" xmlns:ns3="0db41735-03c9-45f7-99e2-dcae27ef4500" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f4c0eefc11dc6e5e719c9a8931b7f89" ns2:_="" ns3:_="">
     <xsd:import namespace="856a7437-a7e7-4452-817c-46e435f59c4c"/>
@@ -31128,10 +31197,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
+    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31148,20 +31248,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
-    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F28B58F-825A-4A47-A022-78D2B46BC906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60352FDB-62EE-41A3-83D4-89B318F32F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$173</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294966054" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="78">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -87,15 +87,6 @@
   </si>
   <si>
     <t>00-LL-00-0015</t>
-  </si>
-  <si>
-    <t>LL-20-3250</t>
-  </si>
-  <si>
-    <t>LL-20-3251</t>
-  </si>
-  <si>
-    <t>LL-20-3255</t>
   </si>
   <si>
     <t>LL-16-3149</t>
@@ -272,9 +263,6 @@
     <t>LL-99-0014</t>
   </si>
   <si>
-    <t>LL-99-0015</t>
-  </si>
-  <si>
     <t>99-9502</t>
   </si>
   <si>
@@ -282,6 +270,9 @@
   </si>
   <si>
     <t>00-LL-00-0013</t>
+  </si>
+  <si>
+    <t>LL-00-0015</t>
   </si>
 </sst>
 </file>
@@ -344,43 +335,13 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <border>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <top/>
@@ -8685,12 +8646,8 @@
             <v/>
           </cell>
           <cell r="J244"/>
-          <cell r="K244" t="str">
-            <v/>
-          </cell>
-          <cell r="L244" t="str">
-            <v/>
-          </cell>
+          <cell r="K244"/>
+          <cell r="L244"/>
           <cell r="M244" t="str">
             <v>N/A</v>
           </cell>
@@ -12838,6 +12795,10 @@
           <cell r="G370" t="str">
             <v>FlowArt: Trace-By-Groove, Coastal Sea Life - DTC Exclusive</v>
           </cell>
+          <cell r="H370" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I370"/>
           <cell r="M370">
             <v>4</v>
           </cell>
@@ -13618,6 +13579,10 @@
           <cell r="G393" t="str">
             <v>FlowArt: Micro Dot #1 - TBD</v>
           </cell>
+          <cell r="H393" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I393"/>
           <cell r="M393">
             <v>4</v>
           </cell>
@@ -13638,6 +13603,10 @@
           <cell r="G394" t="str">
             <v>FlowArt: Micro Dot #2 - TBD</v>
           </cell>
+          <cell r="H394" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I394"/>
           <cell r="M394">
             <v>4</v>
           </cell>
@@ -13658,6 +13627,10 @@
           <cell r="G395" t="str">
             <v>FlowArt: Dot-By-Pattern #1 [Glitter]</v>
           </cell>
+          <cell r="H395" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I395"/>
           <cell r="M395">
             <v>4</v>
           </cell>
@@ -14263,6 +14236,10 @@
           <cell r="G413" t="str">
             <v>FlowArt: Stitch-to-Quilt, Modern Quilts</v>
           </cell>
+          <cell r="H413" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I413"/>
           <cell r="M413">
             <v>4</v>
           </cell>
@@ -14489,6 +14466,10 @@
           <cell r="G420" t="str">
             <v>FlowArt: Premium: Cross-Stitch #1</v>
           </cell>
+          <cell r="H420" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I420"/>
           <cell r="M420">
             <v>4</v>
           </cell>
@@ -14509,6 +14490,10 @@
           <cell r="G421" t="str">
             <v>FlowArt: Large Format: Cross-Stitch #1</v>
           </cell>
+          <cell r="H421" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I421"/>
           <cell r="M421">
             <v>4</v>
           </cell>
@@ -14529,6 +14514,10 @@
           <cell r="G422" t="str">
             <v>FlowArt: Premium: Trace-By-Line #1</v>
           </cell>
+          <cell r="H422" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I422"/>
           <cell r="M422">
             <v>4</v>
           </cell>
@@ -15241,6 +15230,10 @@
           <cell r="G443" t="str">
             <v>FlowArt: Mini Single - Dot-By-Letter [Neon] #1</v>
           </cell>
+          <cell r="H443" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I443"/>
           <cell r="M443">
             <v>6</v>
           </cell>
@@ -15261,6 +15254,10 @@
           <cell r="G444" t="str">
             <v>FlowArt: Mini Single - Dot-By-Letter [Neon] #2</v>
           </cell>
+          <cell r="H444" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I444"/>
           <cell r="M444">
             <v>6</v>
           </cell>
@@ -15281,6 +15278,10 @@
           <cell r="G445" t="str">
             <v>FlowArt: Mini Single - Dot-By-Letter [Neon] #3</v>
           </cell>
+          <cell r="H445" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I445"/>
           <cell r="M445">
             <v>6</v>
           </cell>
@@ -15326,6 +15327,10 @@
           <cell r="G447" t="str">
             <v>FlowArt: Mini Single - Sweet Treats &amp; Dessert Shop #1</v>
           </cell>
+          <cell r="H447" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I447"/>
           <cell r="L447"/>
           <cell r="M447">
             <v>6</v>
@@ -15347,6 +15352,10 @@
           <cell r="G448" t="str">
             <v>FlowArt: Mini Single - Sweet Treats &amp; Dessert Shop #2</v>
           </cell>
+          <cell r="H448" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I448"/>
           <cell r="M448">
             <v>6</v>
           </cell>
@@ -15367,6 +15376,10 @@
           <cell r="G449" t="str">
             <v>FlowArt: Mini Single - Sweet Treats &amp; Dessert Shop #3</v>
           </cell>
+          <cell r="H449" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I449"/>
           <cell r="M449">
             <v>6</v>
           </cell>
@@ -15412,6 +15425,10 @@
           <cell r="G451" t="str">
             <v>FlowArt: Mini Single - Animals #1</v>
           </cell>
+          <cell r="H451" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I451"/>
           <cell r="M451">
             <v>6</v>
           </cell>
@@ -15432,6 +15449,10 @@
           <cell r="G452" t="str">
             <v>FlowArt: Mini Single - Animals #2</v>
           </cell>
+          <cell r="H452" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I452"/>
           <cell r="M452">
             <v>6</v>
           </cell>
@@ -15452,6 +15473,10 @@
           <cell r="G453" t="str">
             <v>FlowArt: Mini Single - Animals #3</v>
           </cell>
+          <cell r="H453" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I453"/>
           <cell r="M453">
             <v>6</v>
           </cell>
@@ -15497,6 +15522,10 @@
           <cell r="G455" t="str">
             <v>FlowArt: Mini Single - Fall Trace-By-Line #1</v>
           </cell>
+          <cell r="H455" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I455"/>
           <cell r="L455"/>
           <cell r="M455">
             <v>6</v>
@@ -15518,6 +15547,10 @@
           <cell r="G456" t="str">
             <v>FlowArt: Mini Single - Fall Trace-By-Line #2</v>
           </cell>
+          <cell r="H456" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I456"/>
           <cell r="M456">
             <v>6</v>
           </cell>
@@ -15538,6 +15571,10 @@
           <cell r="G457" t="str">
             <v>FlowArt: Mini Single - Fall Trace-By-Line #3</v>
           </cell>
+          <cell r="H457" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I457"/>
           <cell r="M457">
             <v>6</v>
           </cell>
@@ -15583,6 +15620,10 @@
           <cell r="G459" t="str">
             <v>FlowArt: Mini Single - Halloween Dot-By-Letter #1</v>
           </cell>
+          <cell r="H459" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I459"/>
           <cell r="M459">
             <v>6</v>
           </cell>
@@ -15603,6 +15644,10 @@
           <cell r="G460" t="str">
             <v>FlowArt: Mini Single - Halloween Dot-By-Letter #2</v>
           </cell>
+          <cell r="H460" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I460"/>
           <cell r="M460">
             <v>6</v>
           </cell>
@@ -15623,6 +15668,10 @@
           <cell r="G461" t="str">
             <v>FlowArt: Mini Single - Halloween Dot-By-Letter #3</v>
           </cell>
+          <cell r="H461" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I461"/>
           <cell r="M461">
             <v>6</v>
           </cell>
@@ -15808,6 +15857,10 @@
           <cell r="G467" t="str">
             <v>FlowArt: Mini, Holiday Cross-Stitch Retail 3Pck</v>
           </cell>
+          <cell r="H467" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I467"/>
           <cell r="L467"/>
           <cell r="M467">
             <v>4</v>
@@ -15829,6 +15882,10 @@
           <cell r="G468" t="str">
             <v>FlowArt: Mini Single - Holiday Cross-Stitch #1</v>
           </cell>
+          <cell r="H468" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I468"/>
           <cell r="M468">
             <v>6</v>
           </cell>
@@ -15849,6 +15906,10 @@
           <cell r="G469" t="str">
             <v>FlowArt: Mini Single - Holiday Cross-Stitch #2</v>
           </cell>
+          <cell r="H469" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I469"/>
           <cell r="M469">
             <v>6</v>
           </cell>
@@ -16489,6 +16550,10 @@
           <cell r="G488" t="str">
             <v>FlowArt: Mini, Fall Trace-By-Line ECOMM 3Pck</v>
           </cell>
+          <cell r="H488" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I488"/>
           <cell r="O488">
             <v>29.99</v>
           </cell>
@@ -16503,6 +16568,10 @@
           <cell r="G489" t="str">
             <v>FlowArt: Mini, Dot-By-Letter [Neon] ECOMM 3Pck</v>
           </cell>
+          <cell r="H489" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I489"/>
           <cell r="O489">
             <v>22.99</v>
           </cell>
@@ -16517,6 +16586,10 @@
           <cell r="G490" t="str">
             <v>FlowArt: Mini, Halloween Dot-By-Letter ECOMM 3Pck</v>
           </cell>
+          <cell r="H490" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I490"/>
           <cell r="O490">
             <v>29.99</v>
           </cell>
@@ -17650,6 +17723,21 @@
           <cell r="G524" t="str">
             <v>FlowArt Mini EXPRESS: Dimensional Tracing #2</v>
           </cell>
+          <cell r="H524" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="I524" t="str">
+            <v>744</v>
+          </cell>
+          <cell r="J524">
+            <v>810076217444</v>
+          </cell>
+          <cell r="K524">
+            <v>50810076217449</v>
+          </cell>
+          <cell r="L524">
+            <v>30810076217445</v>
+          </cell>
           <cell r="M524">
             <v>6</v>
           </cell>
@@ -17695,6 +17783,10 @@
           <cell r="G526" t="str">
             <v>FlowArt Mini EXPRESS: Fall Dot-By-Letter #1</v>
           </cell>
+          <cell r="H526" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I526"/>
           <cell r="M526">
             <v>6</v>
           </cell>
@@ -17715,6 +17807,10 @@
           <cell r="G527" t="str">
             <v>FlowArt Mini EXPRESS: Fall Dot-By-Letter #2</v>
           </cell>
+          <cell r="H527" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I527"/>
           <cell r="M527">
             <v>6</v>
           </cell>
@@ -17735,6 +17831,10 @@
           <cell r="G528" t="str">
             <v>FlowArt Mini EXPRESS: Fall Dot-By-Letter #3</v>
           </cell>
+          <cell r="H528" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I528"/>
           <cell r="M528">
             <v>6</v>
           </cell>
@@ -19597,6 +19697,10 @@
           <cell r="G586" t="str">
             <v>FlowArt 3Pck: Trace-By-Groove, Flowers + Coastal Sea Life + TBD - ECOMM</v>
           </cell>
+          <cell r="H586" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I586"/>
           <cell r="O586">
             <v>29.99</v>
           </cell>
@@ -19991,13 +20095,13 @@
           </cell>
           <cell r="M598"/>
           <cell r="N598">
-            <v>12</v>
+            <v>14</v>
           </cell>
           <cell r="O598">
-            <v>49.99</v>
+            <v>29.99</v>
           </cell>
           <cell r="P598">
-            <v>24.995000000000001</v>
+            <v>14.994999999999999</v>
           </cell>
         </row>
         <row r="599">
@@ -20024,13 +20128,13 @@
           </cell>
           <cell r="M599"/>
           <cell r="N599">
-            <v>12</v>
+            <v>14</v>
           </cell>
           <cell r="O599">
-            <v>49.99</v>
+            <v>29.99</v>
           </cell>
           <cell r="P599">
-            <v>24.995000000000001</v>
+            <v>14.994999999999999</v>
           </cell>
         </row>
         <row r="600">
@@ -20092,13 +20196,13 @@
             <v>4</v>
           </cell>
           <cell r="N601">
-            <v>16</v>
+            <v>12</v>
           </cell>
           <cell r="O601">
-            <v>14.99</v>
+            <v>49.99</v>
           </cell>
           <cell r="P601">
-            <v>7.4950000000000001</v>
+            <v>24.995000000000001</v>
           </cell>
         </row>
         <row r="602">
@@ -20127,13 +20231,13 @@
             <v>4</v>
           </cell>
           <cell r="N602">
-            <v>16</v>
+            <v>12</v>
           </cell>
           <cell r="O602">
-            <v>14.99</v>
+            <v>49.99</v>
           </cell>
           <cell r="P602">
-            <v>7.4950000000000001</v>
+            <v>24.995000000000001</v>
           </cell>
         </row>
         <row r="603">
@@ -20262,6 +20366,10 @@
           <cell r="G608" t="str">
             <v>Palm Calms Gift Set - 6Pck</v>
           </cell>
+          <cell r="H608" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I608"/>
           <cell r="O608">
             <v>29.99</v>
           </cell>
@@ -20333,10 +20441,10 @@
             <v>24</v>
           </cell>
           <cell r="O610">
-            <v>6.97</v>
+            <v>29.99</v>
           </cell>
           <cell r="P610">
-            <v>3.4849999999999999</v>
+            <v>14.994999999999999</v>
           </cell>
         </row>
         <row r="611">
@@ -20486,6 +20594,27 @@
           <cell r="G615" t="str">
             <v>FlowArt: Walmart Exclusive Mini - TBD</v>
           </cell>
+          <cell r="H615" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I615" t="str">
+            <v>699</v>
+          </cell>
+          <cell r="J615">
+            <v>810076216997</v>
+          </cell>
+          <cell r="K615">
+            <v>50810076216992</v>
+          </cell>
+          <cell r="L615">
+            <v>30810076216998</v>
+          </cell>
+          <cell r="M615">
+            <v>6</v>
+          </cell>
+          <cell r="N615">
+            <v>24</v>
+          </cell>
           <cell r="O615">
             <v>6.97</v>
           </cell>
@@ -20557,10 +20686,10 @@
             <v>12</v>
           </cell>
           <cell r="O617">
-            <v>9.94</v>
+            <v>6.97</v>
           </cell>
           <cell r="P617">
-            <v>4.97</v>
+            <v>3.4849999999999999</v>
           </cell>
         </row>
         <row r="618">
@@ -20864,10 +20993,10 @@
             <v/>
           </cell>
           <cell r="O626">
-            <v>19.989999999999998</v>
+            <v>24.99</v>
           </cell>
           <cell r="P626">
-            <v>9.9949999999999992</v>
+            <v>12.494999999999999</v>
           </cell>
         </row>
         <row r="627">
@@ -20896,10 +21025,10 @@
             <v>24</v>
           </cell>
           <cell r="O627">
-            <v>22.99</v>
+            <v>24.99</v>
           </cell>
           <cell r="P627">
-            <v>11.494999999999999</v>
+            <v>12.494999999999999</v>
           </cell>
         </row>
         <row r="628">
@@ -20963,13 +21092,13 @@
             <v>4</v>
           </cell>
           <cell r="N629">
-            <v>12</v>
+            <v>24</v>
           </cell>
           <cell r="O629">
-            <v>12.99</v>
+            <v>22.99</v>
           </cell>
           <cell r="P629">
-            <v>6.4950000000000001</v>
+            <v>11.494999999999999</v>
           </cell>
         </row>
         <row r="630">
@@ -21031,6 +21160,12 @@
           </cell>
           <cell r="M631"/>
           <cell r="N631"/>
+          <cell r="O631">
+            <v>12.99</v>
+          </cell>
+          <cell r="P631">
+            <v>6.4950000000000001</v>
+          </cell>
         </row>
         <row r="632">
           <cell r="F632" t="str">
@@ -21154,10 +21289,10 @@
             <v>12</v>
           </cell>
           <cell r="O635">
-            <v>19.989999999999998</v>
+            <v>0</v>
           </cell>
           <cell r="P635">
-            <v>9.9949999999999992</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="636">
@@ -21189,10 +21324,10 @@
             <v>12</v>
           </cell>
           <cell r="O636">
-            <v>19.989999999999998</v>
+            <v>0</v>
           </cell>
           <cell r="P636">
-            <v>9.9949999999999992</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="637">
@@ -21482,6 +21617,27 @@
           <cell r="G645" t="str">
             <v>Sensory Journal - TBD</v>
           </cell>
+          <cell r="H645" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I645" t="str">
+            <v>526</v>
+          </cell>
+          <cell r="J645">
+            <v>810076215266</v>
+          </cell>
+          <cell r="K645">
+            <v>50810076215261</v>
+          </cell>
+          <cell r="L645">
+            <v>30810076215267</v>
+          </cell>
+          <cell r="M645">
+            <v>4</v>
+          </cell>
+          <cell r="N645">
+            <v>12</v>
+          </cell>
           <cell r="O645">
             <v>12.99</v>
           </cell>
@@ -21553,10 +21709,10 @@
             <v>12</v>
           </cell>
           <cell r="O647">
-            <v>29.99</v>
+            <v>12.99</v>
           </cell>
           <cell r="P647">
-            <v>14.994999999999999</v>
+            <v>6.4950000000000001</v>
           </cell>
         </row>
         <row r="648">
@@ -21616,6 +21772,12 @@
           <cell r="L649">
             <v>30810076213843</v>
           </cell>
+          <cell r="M649">
+            <v>4</v>
+          </cell>
+          <cell r="N649">
+            <v>12</v>
+          </cell>
           <cell r="O649">
             <v>12.99</v>
           </cell>
@@ -21683,9 +21845,11 @@
           <cell r="M651"/>
           <cell r="N651"/>
           <cell r="O651">
-            <v>29.99</v>
-          </cell>
-          <cell r="P651"/>
+            <v>12.99</v>
+          </cell>
+          <cell r="P651">
+            <v>6.4950000000000001</v>
+          </cell>
         </row>
         <row r="652">
           <cell r="F652" t="str">
@@ -21799,7 +21963,7 @@
           <cell r="M655"/>
           <cell r="N655"/>
           <cell r="O655">
-            <v>39.99</v>
+            <v>29.99</v>
           </cell>
           <cell r="P655"/>
         </row>
@@ -21828,7 +21992,7 @@
           <cell r="M656"/>
           <cell r="N656"/>
           <cell r="O656">
-            <v>39.99</v>
+            <v>29.99</v>
           </cell>
           <cell r="P656"/>
         </row>
@@ -21915,7 +22079,7 @@
           <cell r="M659"/>
           <cell r="N659"/>
           <cell r="O659">
-            <v>49.99</v>
+            <v>39.99</v>
           </cell>
           <cell r="P659"/>
         </row>
@@ -21944,7 +22108,7 @@
           <cell r="M660"/>
           <cell r="N660"/>
           <cell r="O660">
-            <v>49.99</v>
+            <v>39.99</v>
           </cell>
           <cell r="P660"/>
         </row>
@@ -22002,7 +22166,7 @@
           <cell r="M662"/>
           <cell r="N662"/>
           <cell r="O662">
-            <v>79.989999999999995</v>
+            <v>49.99</v>
           </cell>
         </row>
         <row r="663">
@@ -22030,7 +22194,7 @@
           <cell r="M663"/>
           <cell r="N663"/>
           <cell r="O663">
-            <v>99.99</v>
+            <v>49.99</v>
           </cell>
         </row>
         <row r="664">
@@ -22125,6 +22289,24 @@
           <cell r="G667" t="str">
             <v>Analog Bag #1</v>
           </cell>
+          <cell r="H667" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I667" t="str">
+            <v>695</v>
+          </cell>
+          <cell r="J667">
+            <v>810076216959</v>
+          </cell>
+          <cell r="K667">
+            <v>50810076216954</v>
+          </cell>
+          <cell r="L667">
+            <v>30810076216950</v>
+          </cell>
+          <cell r="O667">
+            <v>99.99</v>
+          </cell>
         </row>
         <row r="668">
           <cell r="F668" t="str">
@@ -22132,6 +22314,24 @@
           </cell>
           <cell r="G668" t="str">
             <v>Analog Bag #2</v>
+          </cell>
+          <cell r="H668" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I668" t="str">
+            <v>696</v>
+          </cell>
+          <cell r="J668">
+            <v>810076216966</v>
+          </cell>
+          <cell r="K668">
+            <v>50810076216961</v>
+          </cell>
+          <cell r="L668">
+            <v>30810076216967</v>
+          </cell>
+          <cell r="O668">
+            <v>79.989999999999995</v>
           </cell>
         </row>
         <row r="669">
@@ -22270,22 +22470,22 @@
             <v>810076212791</v>
           </cell>
           <cell r="K673">
-            <v>50810076212796</v>
+            <v>60810076212755</v>
           </cell>
           <cell r="L673">
-            <v>30810076212792</v>
+            <v>40810076212751</v>
           </cell>
           <cell r="M673">
             <v>6</v>
           </cell>
           <cell r="N673">
-            <v>18</v>
+            <v>12</v>
           </cell>
           <cell r="O673">
-            <v>8.9600000000000009</v>
+            <v>9.94</v>
           </cell>
           <cell r="P673">
-            <v>4.4800000000000004</v>
+            <v>4.97</v>
           </cell>
         </row>
         <row r="674">
@@ -22960,6 +23160,27 @@
           <cell r="G693" t="str">
             <v>FlowArt: Walmart Exclusive Classic - TBD</v>
           </cell>
+          <cell r="H693" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="I693" t="str">
+            <v>510</v>
+          </cell>
+          <cell r="J693">
+            <v>810076215105</v>
+          </cell>
+          <cell r="K693">
+            <v>50810076215100</v>
+          </cell>
+          <cell r="L693">
+            <v>30810076215106</v>
+          </cell>
+          <cell r="M693">
+            <v>3</v>
+          </cell>
+          <cell r="N693">
+            <v>12</v>
+          </cell>
           <cell r="O693">
             <v>9.94</v>
           </cell>
@@ -22974,6 +23195,27 @@
           <cell r="G694" t="str">
             <v>FlowArt: Classic #1 [Pearl/Luxe] - WMT</v>
           </cell>
+          <cell r="H694" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="I694" t="str">
+            <v>461</v>
+          </cell>
+          <cell r="J694">
+            <v>810076214610</v>
+          </cell>
+          <cell r="K694">
+            <v>50810076214615</v>
+          </cell>
+          <cell r="L694">
+            <v>30810076214611</v>
+          </cell>
+          <cell r="M694">
+            <v>2</v>
+          </cell>
+          <cell r="N694">
+            <v>8</v>
+          </cell>
           <cell r="O694">
             <v>9.94</v>
           </cell>
@@ -22988,6 +23230,10 @@
           <cell r="G695" t="str">
             <v>FlowArt: Classic #2 [Pearl/Luxe] - WMT</v>
           </cell>
+          <cell r="H695" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I695"/>
           <cell r="O695">
             <v>9.94</v>
           </cell>
@@ -23002,6 +23248,10 @@
           <cell r="G696" t="str">
             <v>FlowArt: Classic #3 [Pearl/Luxe] - WMT</v>
           </cell>
+          <cell r="H696" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I696"/>
           <cell r="O696">
             <v>9.94</v>
           </cell>
@@ -23016,6 +23266,10 @@
           <cell r="G697" t="str">
             <v>FlowArt: Classic #4 [Pearl/Luxe] - WMT</v>
           </cell>
+          <cell r="H697" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I697"/>
           <cell r="O697">
             <v>9.94</v>
           </cell>
@@ -23030,6 +23284,10 @@
           <cell r="G698" t="str">
             <v>FlowArt: Classic #5 [Pearl/Luxe] - WMT</v>
           </cell>
+          <cell r="H698" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I698"/>
           <cell r="O698">
             <v>9.94</v>
           </cell>
@@ -23044,6 +23302,16 @@
           <cell r="G699" t="str">
             <v>FlowArt Mini EXPRESS: Holiday #4 - Mode TBD - WMT</v>
           </cell>
+          <cell r="H699" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I699"/>
+          <cell r="O699">
+            <v>9.94</v>
+          </cell>
+          <cell r="P699">
+            <v>4.97</v>
+          </cell>
         </row>
         <row r="700">
           <cell r="F700" t="str">
@@ -23052,6 +23320,16 @@
           <cell r="G700" t="str">
             <v>FlowArt Mini EXPRESS: Holiday #5 - Mode TBD - WMT</v>
           </cell>
+          <cell r="H700" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I700"/>
+          <cell r="O700">
+            <v>9.94</v>
+          </cell>
+          <cell r="P700">
+            <v>4.97</v>
+          </cell>
         </row>
         <row r="701">
           <cell r="F701" t="str">
@@ -23060,6 +23338,10 @@
           <cell r="G701" t="str">
             <v>FlowArt Mini EXPRESS: Holiday #6 - Mode TBD - WMT</v>
           </cell>
+          <cell r="H701" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I701"/>
         </row>
         <row r="702">
           <cell r="F702" t="str">
@@ -23068,6 +23350,10 @@
           <cell r="G702" t="str">
             <v>Palm Calm #1 - TBD - WMT</v>
           </cell>
+          <cell r="H702" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I702"/>
         </row>
         <row r="703">
           <cell r="F703" t="str">
@@ -23076,6 +23362,10 @@
           <cell r="G703" t="str">
             <v>Palm Calm #2 - TBD - WMT</v>
           </cell>
+          <cell r="H703" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I703"/>
         </row>
         <row r="704">
           <cell r="F704" t="str">
@@ -23212,10 +23502,10 @@
           <cell r="M708"/>
           <cell r="N708"/>
           <cell r="O708">
-            <v>199.99</v>
+            <v>79.989999999999995</v>
           </cell>
           <cell r="P708">
-            <v>99.995000000000005</v>
+            <v>39.994999999999997</v>
           </cell>
         </row>
         <row r="709">
@@ -23243,10 +23533,10 @@
           <cell r="M709"/>
           <cell r="N709"/>
           <cell r="O709">
-            <v>429.99</v>
+            <v>79.989999999999995</v>
           </cell>
           <cell r="P709">
-            <v>214.995</v>
+            <v>39.994999999999997</v>
           </cell>
         </row>
         <row r="710">
@@ -23271,6 +23561,12 @@
           <cell r="L710" t="str">
             <v/>
           </cell>
+          <cell r="O710">
+            <v>199.99</v>
+          </cell>
+          <cell r="P710">
+            <v>99.995000000000005</v>
+          </cell>
         </row>
         <row r="711">
           <cell r="F711" t="str">
@@ -23294,6 +23590,12 @@
           <cell r="L711" t="str">
             <v/>
           </cell>
+          <cell r="O711">
+            <v>429.99</v>
+          </cell>
+          <cell r="P711">
+            <v>214.995</v>
+          </cell>
         </row>
         <row r="712">
           <cell r="F712" t="str">
@@ -23529,6 +23831,9 @@
           <cell r="N719">
             <v>1</v>
           </cell>
+          <cell r="P719">
+            <v>180</v>
+          </cell>
         </row>
         <row r="720">
           <cell r="F720" t="str">
@@ -23543,6 +23848,9 @@
           <cell r="I720" t="str">
             <v/>
           </cell>
+          <cell r="J720"/>
+          <cell r="K720"/>
+          <cell r="L720"/>
           <cell r="M720">
             <v>0</v>
           </cell>
@@ -23578,6 +23886,9 @@
           <cell r="N721">
             <v>1</v>
           </cell>
+          <cell r="P721">
+            <v>252</v>
+          </cell>
         </row>
         <row r="722">
           <cell r="F722" t="str">
@@ -23624,11 +23935,23 @@
           <cell r="I723" t="str">
             <v/>
           </cell>
+          <cell r="J723">
+            <v>810076215785</v>
+          </cell>
+          <cell r="K723">
+            <v>50810076215780</v>
+          </cell>
+          <cell r="L723">
+            <v>30810076215786</v>
+          </cell>
           <cell r="M723">
             <v>0</v>
           </cell>
           <cell r="N723">
             <v>1</v>
+          </cell>
+          <cell r="P723">
+            <v>140</v>
           </cell>
         </row>
         <row r="724">
@@ -23676,6 +23999,15 @@
           <cell r="I725" t="str">
             <v/>
           </cell>
+          <cell r="J725">
+            <v>810076213736</v>
+          </cell>
+          <cell r="K725">
+            <v>50810076213731</v>
+          </cell>
+          <cell r="L725">
+            <v>30810076213737</v>
+          </cell>
           <cell r="M725">
             <v>0</v>
           </cell>
@@ -23888,6 +24220,15 @@
           <cell r="I732" t="str">
             <v/>
           </cell>
+          <cell r="J732">
+            <v>810076217260</v>
+          </cell>
+          <cell r="K732">
+            <v>50810076217265</v>
+          </cell>
+          <cell r="L732">
+            <v>30810076217261</v>
+          </cell>
           <cell r="M732">
             <v>0</v>
           </cell>
@@ -23914,6 +24255,12 @@
           <cell r="J733">
             <v>810076215594</v>
           </cell>
+          <cell r="K733">
+            <v>50810076217272</v>
+          </cell>
+          <cell r="L733">
+            <v>30810076217278</v>
+          </cell>
           <cell r="M733">
             <v>0</v>
           </cell>
@@ -23937,6 +24284,15 @@
           <cell r="I734" t="str">
             <v/>
           </cell>
+          <cell r="J734">
+            <v>810076217284</v>
+          </cell>
+          <cell r="K734">
+            <v>50810076217289</v>
+          </cell>
+          <cell r="L734">
+            <v>30810076217285</v>
+          </cell>
           <cell r="M734">
             <v>0</v>
           </cell>
@@ -24007,6 +24363,9 @@
           <cell r="N736">
             <v>1</v>
           </cell>
+          <cell r="P736">
+            <v>45</v>
+          </cell>
         </row>
         <row r="737">
           <cell r="F737" t="str">
@@ -24068,6 +24427,9 @@
           <cell r="N738">
             <v>1</v>
           </cell>
+          <cell r="P738">
+            <v>0</v>
+          </cell>
         </row>
         <row r="739">
           <cell r="F739" t="str">
@@ -24120,6 +24482,9 @@
           <cell r="N740">
             <v>1</v>
           </cell>
+          <cell r="P740">
+            <v>0</v>
+          </cell>
         </row>
         <row r="741">
           <cell r="F741" t="str">
@@ -24198,11 +24563,23 @@
           <cell r="I743" t="str">
             <v/>
           </cell>
+          <cell r="J743">
+            <v>810076214375</v>
+          </cell>
+          <cell r="K743">
+            <v>50810076214370</v>
+          </cell>
+          <cell r="L743">
+            <v>30810076214376</v>
+          </cell>
           <cell r="M743">
             <v>0</v>
           </cell>
           <cell r="N743">
             <v>1</v>
+          </cell>
+          <cell r="P743">
+            <v>126</v>
           </cell>
         </row>
         <row r="744">
@@ -24264,6 +24641,9 @@
           <cell r="N745">
             <v>1</v>
           </cell>
+          <cell r="P745">
+            <v>21</v>
+          </cell>
         </row>
         <row r="746">
           <cell r="F746" t="str">
@@ -24358,7 +24738,7 @@
             <v>159.84</v>
           </cell>
           <cell r="P748">
-            <v>120</v>
+            <v>126</v>
           </cell>
         </row>
         <row r="749">
@@ -24410,10 +24790,10 @@
             <v>1</v>
           </cell>
           <cell r="O750">
-            <v>159.84</v>
+            <v>0</v>
           </cell>
           <cell r="P750">
-            <v>120</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="751">
@@ -24429,6 +24809,15 @@
           <cell r="I751" t="str">
             <v/>
           </cell>
+          <cell r="J751">
+            <v>810076214405</v>
+          </cell>
+          <cell r="K751">
+            <v>50810076214400</v>
+          </cell>
+          <cell r="L751">
+            <v>30810076214406</v>
+          </cell>
           <cell r="M751">
             <v>0</v>
           </cell>
@@ -24484,11 +24873,23 @@
           <cell r="I753" t="str">
             <v/>
           </cell>
+          <cell r="J753">
+            <v>810076214313</v>
+          </cell>
+          <cell r="K753">
+            <v>50810076214318</v>
+          </cell>
+          <cell r="L753">
+            <v>30810076214314</v>
+          </cell>
           <cell r="M753">
             <v>0</v>
           </cell>
           <cell r="N753">
             <v>1</v>
+          </cell>
+          <cell r="P753">
+            <v>252</v>
           </cell>
         </row>
         <row r="754">
@@ -24504,6 +24905,15 @@
           <cell r="I754" t="str">
             <v/>
           </cell>
+          <cell r="J754">
+            <v>810076215174</v>
+          </cell>
+          <cell r="K754">
+            <v>50810076215179</v>
+          </cell>
+          <cell r="L754">
+            <v>30810076215175</v>
+          </cell>
           <cell r="M754">
             <v>0</v>
           </cell>
@@ -24565,6 +24975,15 @@
           <cell r="I756" t="str">
             <v/>
           </cell>
+          <cell r="J756">
+            <v>810076215181</v>
+          </cell>
+          <cell r="K756">
+            <v>50810076215186</v>
+          </cell>
+          <cell r="L756">
+            <v>30810076215182</v>
+          </cell>
           <cell r="M756">
             <v>0</v>
           </cell>
@@ -24626,6 +25045,15 @@
           <cell r="I758" t="str">
             <v/>
           </cell>
+          <cell r="J758">
+            <v>810076215198</v>
+          </cell>
+          <cell r="K758">
+            <v>50810076215193</v>
+          </cell>
+          <cell r="L758">
+            <v>30810076215199</v>
+          </cell>
           <cell r="M758">
             <v>0</v>
           </cell>
@@ -24713,6 +25141,15 @@
           <cell r="I761" t="str">
             <v/>
           </cell>
+          <cell r="J761">
+            <v>810076215204</v>
+          </cell>
+          <cell r="K761">
+            <v>50810076215209</v>
+          </cell>
+          <cell r="L761">
+            <v>30810076215205</v>
+          </cell>
           <cell r="M761">
             <v>0</v>
           </cell>
@@ -24764,6 +25201,15 @@
           </cell>
           <cell r="I763" t="str">
             <v/>
+          </cell>
+          <cell r="J763">
+            <v>810076215211</v>
+          </cell>
+          <cell r="K763">
+            <v>50810076215216</v>
+          </cell>
+          <cell r="L763">
+            <v>30810076215212</v>
           </cell>
           <cell r="M763">
             <v>0</v>
@@ -24948,6 +25394,12 @@
           <cell r="N769">
             <v>1</v>
           </cell>
+          <cell r="O769">
+            <v>251.64000000000001</v>
+          </cell>
+          <cell r="P769">
+            <v>126</v>
+          </cell>
         </row>
         <row r="770">
           <cell r="F770" t="str">
@@ -24978,10 +25430,10 @@
             <v>1</v>
           </cell>
           <cell r="O770">
-            <v>179.64000000000001</v>
+            <v>251.64000000000001</v>
           </cell>
           <cell r="P770">
-            <v>80.28</v>
+            <v>126</v>
           </cell>
         </row>
         <row r="771">
@@ -25038,6 +25490,12 @@
           <cell r="N772">
             <v>1</v>
           </cell>
+          <cell r="O772">
+            <v>251.64000000000001</v>
+          </cell>
+          <cell r="P772">
+            <v>126</v>
+          </cell>
         </row>
         <row r="773">
           <cell r="F773" t="str">
@@ -25093,6 +25551,12 @@
           <cell r="N774">
             <v>1</v>
           </cell>
+          <cell r="O774">
+            <v>251.64000000000001</v>
+          </cell>
+          <cell r="P774">
+            <v>126</v>
+          </cell>
         </row>
         <row r="775">
           <cell r="F775" t="str">
@@ -25142,11 +25606,26 @@
           <cell r="I776" t="str">
             <v/>
           </cell>
+          <cell r="J776">
+            <v>810076215570</v>
+          </cell>
+          <cell r="K776">
+            <v>50810076215575</v>
+          </cell>
+          <cell r="L776">
+            <v>30810076215571</v>
+          </cell>
           <cell r="M776">
             <v>0</v>
           </cell>
           <cell r="N776">
             <v>1</v>
+          </cell>
+          <cell r="O776">
+            <v>179.64000000000001</v>
+          </cell>
+          <cell r="P776">
+            <v>80.28</v>
           </cell>
         </row>
         <row r="777">
@@ -25243,6 +25722,9 @@
           <cell r="N779">
             <v>1</v>
           </cell>
+          <cell r="O779">
+            <v>143.76</v>
+          </cell>
           <cell r="P779">
             <v>180</v>
           </cell>
@@ -25295,6 +25777,12 @@
           <cell r="N781">
             <v>1</v>
           </cell>
+          <cell r="O781">
+            <v>239.76</v>
+          </cell>
+          <cell r="P781">
+            <v>120</v>
+          </cell>
         </row>
         <row r="782">
           <cell r="F782" t="str">
@@ -25355,6 +25843,12 @@
           </cell>
           <cell r="N783">
             <v>1</v>
+          </cell>
+          <cell r="O783">
+            <v>239.76</v>
+          </cell>
+          <cell r="P783">
+            <v>120</v>
           </cell>
         </row>
         <row r="784">
@@ -25409,7 +25903,9 @@
             <v>100</v>
           </cell>
           <cell r="O785"/>
-          <cell r="P785"/>
+          <cell r="P785">
+            <v>180</v>
+          </cell>
         </row>
         <row r="786">
           <cell r="F786" t="str">
@@ -25453,6 +25949,15 @@
           <cell r="I787" t="str">
             <v/>
           </cell>
+          <cell r="J787">
+            <v>810076213170</v>
+          </cell>
+          <cell r="K787">
+            <v>50810076213175</v>
+          </cell>
+          <cell r="L787">
+            <v>30810076213171</v>
+          </cell>
           <cell r="M787">
             <v>0</v>
           </cell>
@@ -25488,6 +25993,9 @@
           <cell r="N788">
             <v>1</v>
           </cell>
+          <cell r="P788">
+            <v>400</v>
+          </cell>
         </row>
         <row r="789">
           <cell r="F789" t="str">
@@ -25580,6 +26088,15 @@
           <cell r="I792" t="str">
             <v/>
           </cell>
+          <cell r="J792">
+            <v>810076214139</v>
+          </cell>
+          <cell r="K792">
+            <v>50810076214134</v>
+          </cell>
+          <cell r="L792">
+            <v>30810076214130</v>
+          </cell>
           <cell r="M792">
             <v>0</v>
           </cell>
@@ -25619,6 +26136,15 @@
           </cell>
           <cell r="I794" t="str">
             <v/>
+          </cell>
+          <cell r="J794">
+            <v>810076214733</v>
+          </cell>
+          <cell r="K794">
+            <v>50810076214738</v>
+          </cell>
+          <cell r="L794">
+            <v>30810076214734</v>
           </cell>
           <cell r="M794">
             <v>0</v>
@@ -25674,6 +26200,12 @@
           <cell r="L796" t="str">
             <v/>
           </cell>
+          <cell r="M796">
+            <v>0</v>
+          </cell>
+          <cell r="N796">
+            <v>1</v>
+          </cell>
         </row>
         <row r="797">
           <cell r="F797" t="str">
@@ -25697,6 +26229,12 @@
           <cell r="L797" t="str">
             <v/>
           </cell>
+          <cell r="M797">
+            <v>0</v>
+          </cell>
+          <cell r="N797">
+            <v>1</v>
+          </cell>
         </row>
         <row r="798">
           <cell r="F798" t="str">
@@ -25720,6 +26258,12 @@
           <cell r="L798" t="str">
             <v/>
           </cell>
+          <cell r="M798">
+            <v>0</v>
+          </cell>
+          <cell r="N798">
+            <v>1</v>
+          </cell>
         </row>
         <row r="799">
           <cell r="F799" t="str">
@@ -25743,6 +26287,12 @@
           <cell r="L799" t="str">
             <v/>
           </cell>
+          <cell r="M799">
+            <v>0</v>
+          </cell>
+          <cell r="N799">
+            <v>1</v>
+          </cell>
         </row>
         <row r="800">
           <cell r="F800" t="str">
@@ -25766,6 +26316,12 @@
           <cell r="L800" t="str">
             <v/>
           </cell>
+          <cell r="M800">
+            <v>0</v>
+          </cell>
+          <cell r="N800">
+            <v>1</v>
+          </cell>
         </row>
         <row r="801">
           <cell r="F801" t="str">
@@ -25789,6 +26345,12 @@
           <cell r="L801" t="str">
             <v/>
           </cell>
+          <cell r="M801">
+            <v>0</v>
+          </cell>
+          <cell r="N801">
+            <v>1</v>
+          </cell>
         </row>
         <row r="802">
           <cell r="F802" t="str">
@@ -26256,13 +26818,13 @@
             <v>6</v>
           </cell>
           <cell r="N818">
-            <v>24</v>
+            <v>20</v>
           </cell>
           <cell r="O818">
-            <v>6.99</v>
+            <v>29.99</v>
           </cell>
           <cell r="P818">
-            <v>3.4950000000000001</v>
+            <v>14.994999999999999</v>
           </cell>
         </row>
         <row r="819">
@@ -26602,6 +27164,18 @@
           <cell r="L828">
             <v>30810076212860</v>
           </cell>
+          <cell r="M828">
+            <v>6</v>
+          </cell>
+          <cell r="N828">
+            <v>24</v>
+          </cell>
+          <cell r="O828">
+            <v>10</v>
+          </cell>
+          <cell r="P828">
+            <v>5</v>
+          </cell>
         </row>
         <row r="829">
           <cell r="F829" t="str">
@@ -26625,6 +27199,18 @@
           <cell r="L829">
             <v>30810076212747</v>
           </cell>
+          <cell r="M829">
+            <v>6</v>
+          </cell>
+          <cell r="N829">
+            <v>24</v>
+          </cell>
+          <cell r="O829">
+            <v>10</v>
+          </cell>
+          <cell r="P829">
+            <v>5</v>
+          </cell>
         </row>
         <row r="830">
           <cell r="F830" t="str">
@@ -26648,6 +27234,18 @@
           <cell r="L830">
             <v>30810076212853</v>
           </cell>
+          <cell r="M830">
+            <v>6</v>
+          </cell>
+          <cell r="N830">
+            <v>24</v>
+          </cell>
+          <cell r="O830">
+            <v>10</v>
+          </cell>
+          <cell r="P830">
+            <v>5</v>
+          </cell>
         </row>
         <row r="831">
           <cell r="F831" t="str">
@@ -26671,6 +27269,18 @@
           <cell r="L831">
             <v>30810076212785</v>
           </cell>
+          <cell r="M831">
+            <v>6</v>
+          </cell>
+          <cell r="N831">
+            <v>24</v>
+          </cell>
+          <cell r="O831">
+            <v>10</v>
+          </cell>
+          <cell r="P831">
+            <v>5</v>
+          </cell>
         </row>
         <row r="832">
           <cell r="F832" t="str">
@@ -26694,6 +27304,18 @@
           <cell r="L832">
             <v>30810076212778</v>
           </cell>
+          <cell r="M832">
+            <v>6</v>
+          </cell>
+          <cell r="N832">
+            <v>24</v>
+          </cell>
+          <cell r="O832">
+            <v>10</v>
+          </cell>
+          <cell r="P832">
+            <v>5</v>
+          </cell>
         </row>
         <row r="833">
           <cell r="F833" t="str">
@@ -26716,6 +27338,18 @@
           </cell>
           <cell r="L833">
             <v>30810076212884</v>
+          </cell>
+          <cell r="M833">
+            <v>6</v>
+          </cell>
+          <cell r="N833">
+            <v>24</v>
+          </cell>
+          <cell r="O833">
+            <v>10</v>
+          </cell>
+          <cell r="P833">
+            <v>5</v>
           </cell>
         </row>
         <row r="834">
@@ -27025,6 +27659,12 @@
           <cell r="N843" t="str">
             <v/>
           </cell>
+          <cell r="O843">
+            <v>10</v>
+          </cell>
+          <cell r="P843">
+            <v>5</v>
+          </cell>
         </row>
         <row r="844">
           <cell r="F844">
@@ -27054,6 +27694,12 @@
           <cell r="N844" t="str">
             <v/>
           </cell>
+          <cell r="O844">
+            <v>10</v>
+          </cell>
+          <cell r="P844">
+            <v>5</v>
+          </cell>
         </row>
         <row r="845">
           <cell r="F845">
@@ -27083,6 +27729,12 @@
           <cell r="N845" t="str">
             <v/>
           </cell>
+          <cell r="O845">
+            <v>10</v>
+          </cell>
+          <cell r="P845">
+            <v>5</v>
+          </cell>
         </row>
         <row r="846">
           <cell r="F846">
@@ -27112,6 +27764,12 @@
           <cell r="N846" t="str">
             <v/>
           </cell>
+          <cell r="O846">
+            <v>26.99</v>
+          </cell>
+          <cell r="P846">
+            <v>13.494999999999999</v>
+          </cell>
         </row>
         <row r="847">
           <cell r="F847">
@@ -27141,6 +27799,12 @@
           <cell r="N847" t="str">
             <v/>
           </cell>
+          <cell r="O847">
+            <v>14.99</v>
+          </cell>
+          <cell r="P847">
+            <v>7.4950000000000001</v>
+          </cell>
         </row>
         <row r="848">
           <cell r="F848">
@@ -27170,6 +27834,12 @@
           <cell r="N848" t="str">
             <v/>
           </cell>
+          <cell r="O848">
+            <v>14.99</v>
+          </cell>
+          <cell r="P848">
+            <v>7.4950000000000001</v>
+          </cell>
         </row>
         <row r="849">
           <cell r="F849">
@@ -27222,6 +27892,8 @@
           <cell r="L850" t="str">
             <v/>
           </cell>
+          <cell r="M850"/>
+          <cell r="N850"/>
         </row>
         <row r="851">
           <cell r="F851" t="str">
@@ -27245,6 +27917,8 @@
           <cell r="L851" t="str">
             <v/>
           </cell>
+          <cell r="M851"/>
+          <cell r="N851"/>
         </row>
         <row r="852">
           <cell r="F852" t="str">
@@ -27268,6 +27942,8 @@
           <cell r="L852" t="str">
             <v/>
           </cell>
+          <cell r="M852"/>
+          <cell r="N852"/>
         </row>
         <row r="853">
           <cell r="F853" t="str">
@@ -27291,6 +27967,8 @@
           <cell r="L853" t="str">
             <v/>
           </cell>
+          <cell r="M853"/>
+          <cell r="N853"/>
         </row>
         <row r="854">
           <cell r="F854" t="str">
@@ -27314,6 +27992,8 @@
           <cell r="L854" t="str">
             <v/>
           </cell>
+          <cell r="M854"/>
+          <cell r="N854"/>
         </row>
         <row r="855">
           <cell r="F855" t="str">
@@ -27547,6 +28227,12 @@
           <cell r="I862" t="str">
             <v/>
           </cell>
+          <cell r="J862">
+            <v>810076212265</v>
+          </cell>
+          <cell r="K862">
+            <v>50810076212260</v>
+          </cell>
           <cell r="L862" t="str">
             <v/>
           </cell>
@@ -27579,6 +28265,12 @@
           <cell r="L863" t="str">
             <v/>
           </cell>
+          <cell r="M863">
+            <v>4</v>
+          </cell>
+          <cell r="N863">
+            <v>12</v>
+          </cell>
           <cell r="O863">
             <v>11.99</v>
           </cell>
@@ -27590,6 +28282,9 @@
           <cell r="F864" t="str">
             <v>112522</v>
           </cell>
+          <cell r="G864" t="str">
+            <v>Lifelines Frosted Cream Candle with Clickwick (11-1603 &amp; 110455 Woodsy)</v>
+          </cell>
           <cell r="H864" t="str">
             <v>N</v>
           </cell>
@@ -27612,10 +28307,10 @@
             <v/>
           </cell>
           <cell r="O864">
-            <v>9.99</v>
+            <v>41.98</v>
           </cell>
           <cell r="P864">
-            <v>4.9950000000000001</v>
+            <v>20.99</v>
           </cell>
         </row>
         <row r="865">
@@ -27647,10 +28342,10 @@
             <v>1</v>
           </cell>
           <cell r="O865">
-            <v>300</v>
+            <v>41.98</v>
           </cell>
           <cell r="P865">
-            <v>150</v>
+            <v>20.99</v>
           </cell>
         </row>
         <row r="866">
@@ -27660,6 +28355,23 @@
           <cell r="G866" t="str">
             <v>DIFFUSER, LED,Winter Edition (Frosted Green)</v>
           </cell>
+          <cell r="H866" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I866" t="str">
+            <v>141</v>
+          </cell>
+          <cell r="J866">
+            <v>810076211411</v>
+          </cell>
+          <cell r="K866"/>
+          <cell r="L866"/>
+          <cell r="O866">
+            <v>41.98</v>
+          </cell>
+          <cell r="P866">
+            <v>20.99</v>
+          </cell>
         </row>
         <row r="867">
           <cell r="F867" t="str">
@@ -27668,6 +28380,23 @@
           <cell r="G867" t="str">
             <v>Candle + Oil  BOX Set  (4 oils) - Frosted Cream Candle</v>
           </cell>
+          <cell r="H867" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="I867" t="str">
+            <v>047</v>
+          </cell>
+          <cell r="J867">
+            <v>810076210476</v>
+          </cell>
+          <cell r="K867"/>
+          <cell r="L867"/>
+          <cell r="O867">
+            <v>11.99</v>
+          </cell>
+          <cell r="P867">
+            <v>5.9950000000000001</v>
+          </cell>
         </row>
         <row r="868">
           <cell r="F868" t="str">
@@ -27688,9 +28417,7 @@
           <cell r="K868">
             <v>50810076214578</v>
           </cell>
-          <cell r="L868">
-            <v>30810076214574</v>
-          </cell>
+          <cell r="L868"/>
           <cell r="M868">
             <v>4</v>
           </cell>
@@ -27698,10 +28425,10 @@
             <v>12</v>
           </cell>
           <cell r="O868">
-            <v>15</v>
+            <v>11.99</v>
           </cell>
           <cell r="P868">
-            <v>7.5</v>
+            <v>5.9950000000000001</v>
           </cell>
         </row>
         <row r="869">
@@ -27733,10 +28460,10 @@
             <v>12</v>
           </cell>
           <cell r="O869">
-            <v>15</v>
+            <v>11.99</v>
           </cell>
           <cell r="P869">
-            <v>7.5</v>
+            <v>5.9950000000000001</v>
           </cell>
         </row>
         <row r="870">
@@ -27750,28 +28477,20 @@
             <v>N</v>
           </cell>
           <cell r="I870" t="str">
-            <v>463</v>
+            <v>193</v>
           </cell>
           <cell r="J870">
-            <v>810076214634</v>
-          </cell>
-          <cell r="K870">
-            <v>50810076214639</v>
-          </cell>
-          <cell r="L870">
-            <v>30810076214635</v>
-          </cell>
-          <cell r="M870">
-            <v>4</v>
-          </cell>
-          <cell r="N870">
-            <v>12</v>
-          </cell>
+            <v>810076211930</v>
+          </cell>
+          <cell r="K870"/>
+          <cell r="L870"/>
+          <cell r="M870"/>
+          <cell r="N870"/>
           <cell r="O870">
-            <v>15</v>
+            <v>9.99</v>
           </cell>
           <cell r="P870">
-            <v>7.5</v>
+            <v>4.9950000000000001</v>
           </cell>
         </row>
         <row r="871">
@@ -27949,8 +28668,223 @@
             <v>5</v>
           </cell>
         </row>
+        <row r="876">
+          <cell r="F876" t="str">
+            <v>LL-25-3283</v>
+          </cell>
+          <cell r="G876" t="str">
+            <v>Scented Palm Calms 4 - Zen Meditation - WMT</v>
+          </cell>
+          <cell r="H876" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I876" t="str">
+            <v>463</v>
+          </cell>
+          <cell r="J876">
+            <v>810076214634</v>
+          </cell>
+          <cell r="K876">
+            <v>50810076214639</v>
+          </cell>
+          <cell r="L876">
+            <v>30810076214635</v>
+          </cell>
+          <cell r="M876">
+            <v>4</v>
+          </cell>
+          <cell r="N876">
+            <v>12</v>
+          </cell>
+          <cell r="O876">
+            <v>15</v>
+          </cell>
+          <cell r="P876">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="877">
+          <cell r="F877" t="str">
+            <v>LL-25-3284</v>
+          </cell>
+          <cell r="G877" t="str">
+            <v>Scented Palm Calms 5 - Forest Friends - WMT</v>
+          </cell>
+          <cell r="H877" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I877" t="str">
+            <v>464</v>
+          </cell>
+          <cell r="J877">
+            <v>810076214641</v>
+          </cell>
+          <cell r="K877">
+            <v>50810076214646</v>
+          </cell>
+          <cell r="L877">
+            <v>30810076214642</v>
+          </cell>
+          <cell r="M877">
+            <v>4</v>
+          </cell>
+          <cell r="N877">
+            <v>12</v>
+          </cell>
+          <cell r="O877">
+            <v>15</v>
+          </cell>
+          <cell r="P877">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="878">
+          <cell r="F878" t="str">
+            <v>LL-25-3285</v>
+          </cell>
+          <cell r="G878" t="str">
+            <v>Scented Palm Calms 6 - Animal Friends - WMT</v>
+          </cell>
+          <cell r="H878" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I878" t="str">
+            <v>465</v>
+          </cell>
+          <cell r="J878">
+            <v>810076214658</v>
+          </cell>
+          <cell r="K878">
+            <v>50810076214653</v>
+          </cell>
+          <cell r="L878">
+            <v>30810076214659</v>
+          </cell>
+          <cell r="M878">
+            <v>4</v>
+          </cell>
+          <cell r="N878">
+            <v>12</v>
+          </cell>
+          <cell r="O878">
+            <v>15</v>
+          </cell>
+          <cell r="P878">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="879">
+          <cell r="F879" t="str">
+            <v>LL-25-3286</v>
+          </cell>
+          <cell r="G879" t="str">
+            <v>Scented Palm Calms 7 - Writers Desk -  WMT</v>
+          </cell>
+          <cell r="H879" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I879" t="str">
+            <v>466</v>
+          </cell>
+          <cell r="J879">
+            <v>810076214665</v>
+          </cell>
+          <cell r="K879">
+            <v>50810076214660</v>
+          </cell>
+          <cell r="L879">
+            <v>30810076214666</v>
+          </cell>
+          <cell r="M879">
+            <v>4</v>
+          </cell>
+          <cell r="N879">
+            <v>12</v>
+          </cell>
+          <cell r="O879">
+            <v>15</v>
+          </cell>
+          <cell r="P879">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="880">
+          <cell r="F880" t="str">
+            <v>LL-25-3287</v>
+          </cell>
+          <cell r="G880" t="str">
+            <v>Scented Palm Calms 8 - Little Books -  WMT</v>
+          </cell>
+          <cell r="H880" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I880" t="str">
+            <v>467</v>
+          </cell>
+          <cell r="J880">
+            <v>810076214672</v>
+          </cell>
+          <cell r="K880">
+            <v>50810076214677</v>
+          </cell>
+          <cell r="L880">
+            <v>30810076214673</v>
+          </cell>
+          <cell r="M880">
+            <v>4</v>
+          </cell>
+          <cell r="N880">
+            <v>12</v>
+          </cell>
+          <cell r="O880">
+            <v>15</v>
+          </cell>
+          <cell r="P880">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="881">
+          <cell r="F881" t="str">
+            <v>LL-25-3278</v>
+          </cell>
+          <cell r="G881" t="str">
+            <v>Scented Palm Calms Discovery Set - WMT</v>
+          </cell>
+          <cell r="H881" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I881" t="str">
+            <v>460</v>
+          </cell>
+          <cell r="J881">
+            <v>810076214603</v>
+          </cell>
+          <cell r="K881">
+            <v>50810076214608</v>
+          </cell>
+          <cell r="L881">
+            <v>30810076214604</v>
+          </cell>
+          <cell r="M881">
+            <v>4</v>
+          </cell>
+          <cell r="N881">
+            <v>12</v>
+          </cell>
+          <cell r="O881">
+            <v>10</v>
+          </cell>
+          <cell r="P881">
+            <v>5</v>
+          </cell>
+        </row>
         <row r="1500">
           <cell r="F1500" t="str">
+            <v>=IF(RC5=RC1, "", VLOOKUP(RC5, SBOM!C6:C7, 2, FALSE))</v>
+          </cell>
+        </row>
+        <row r="1506">
+          <cell r="F1506" t="str">
             <v>=IF(RC5=RC1, "", VLOOKUP(RC5, SBOM!C6:C7, 2, FALSE))</v>
           </cell>
         </row>
@@ -28147,7 +29081,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.9375" bestFit="1" customWidth="1"/>
@@ -28159,24 +29093,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -28189,7 +29123,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -28200,13 +29134,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D5" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C5, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C5), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28222,7 +29156,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B6">
         <f>IF(A5=A6, B5+1, 1)</f>
@@ -28245,7 +29179,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B7">
         <f t="shared" ref="B7:B70" si="0">IF(A6=A7, B6+1, 1)</f>
@@ -28268,7 +29202,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
@@ -28291,7 +29225,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -28314,7 +29248,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -28337,7 +29271,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -28360,14 +29294,14 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C12), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28376,20 +29310,20 @@
       <c r="E12">
         <v>12</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D13" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C13), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28398,20 +29332,20 @@
       <c r="E13">
         <v>4</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D14" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C14), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28422,19 +29356,19 @@
       </c>
       <c r="F14" s="2">
         <f>IF(IF(RIGHT($A14,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A14,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D15" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C15), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28443,20 +29377,20 @@
       <c r="E15">
         <v>12</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D16" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C16), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28465,20 +29399,20 @@
       <c r="E16">
         <v>12</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D17" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C17), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28487,20 +29421,20 @@
       <c r="E17">
         <v>12</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D18" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C18), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28509,20 +29443,20 @@
       <c r="E18">
         <v>4</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D19" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C19), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28531,20 +29465,20 @@
       <c r="E19">
         <v>12</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D20" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C20), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28553,20 +29487,20 @@
       <c r="E20">
         <v>12</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D21" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C21), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28575,20 +29509,20 @@
       <c r="E21">
         <v>8</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D22" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C22), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28597,20 +29531,20 @@
       <c r="E22">
         <v>4</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D23" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C23), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28619,20 +29553,20 @@
       <c r="E23">
         <v>12</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D24" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C24), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28641,20 +29575,20 @@
       <c r="E24">
         <v>12</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D25" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C25), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28663,20 +29597,20 @@
       <c r="E25">
         <v>16</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D26" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C26), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28685,20 +29619,20 @@
       <c r="E26">
         <v>8</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D27" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C27), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28707,20 +29641,20 @@
       <c r="E27">
         <v>4</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D28" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C28), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28729,20 +29663,20 @@
       <c r="E28">
         <v>4</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D29" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C29), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28758,7 +29692,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
@@ -28781,7 +29715,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
@@ -28804,7 +29738,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
@@ -28827,7 +29761,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
@@ -28850,7 +29784,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
@@ -28873,7 +29807,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
@@ -28896,14 +29830,14 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D36" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C36), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28919,14 +29853,14 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D37" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C37), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28942,14 +29876,14 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D38" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C38), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28965,14 +29899,14 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D39" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C39), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -28988,14 +29922,14 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D40" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C40), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29011,14 +29945,14 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D41" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C41), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29034,14 +29968,14 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D42" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C42), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29057,14 +29991,14 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D43" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C43), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29080,14 +30014,14 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D44" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29103,14 +30037,14 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D45" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29126,14 +30060,14 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D46" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C46), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29149,14 +30083,14 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D47" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C47), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29179,7 +30113,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D48" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C48), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -29344,122 +30278,122 @@
       </c>
       <c r="D55" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C55), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Holiday Mini - Counter Display - Empty</v>
+        <v>FA Holiday Mini - Counter Display - Full</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55" s="2">
         <f>IF(IF(RIGHT($A55,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A55,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="D56" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+        <v>Pen Display - Empty</v>
       </c>
       <c r="E56">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F56" s="2">
         <f>IF(IF(RIGHT($A56,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A56,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D57" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C57), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E57">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F57" s="2">
         <f>IF(IF(RIGHT($A57,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A57,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D58" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E58">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F58" s="2">
         <f>IF(IF(RIGHT($A58,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A58,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="D59" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Display - Empty</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" s="2">
         <f>IF(IF(RIGHT($A59,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A59,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D60" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E60">
         <v>8</v>
@@ -29471,21 +30405,21 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D61" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F61" s="2">
         <f>IF(IF(RIGHT($A61,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A61,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29494,18 +30428,18 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D62" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E62">
         <v>4</v>
@@ -29517,21 +30451,21 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B63">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D63" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E63">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F63" s="2">
         <f>IF(IF(RIGHT($A63,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A63,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29540,21 +30474,21 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" s="2">
         <f>IF(IF(RIGHT($A64,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A64,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29563,18 +30497,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="D65" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -29586,18 +30520,18 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B66">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E66">
         <v>4</v>
@@ -29609,21 +30543,21 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E67">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="2">
         <f>IF(IF(RIGHT($A67,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A67,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29632,21 +30566,21 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B68">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F68" s="2">
         <f>IF(IF(RIGHT($A68,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A68,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29655,21 +30589,21 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B69">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D69" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F69" s="2">
         <f>IF(IF(RIGHT($A69,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A69,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29678,18 +30612,18 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B70">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E70">
         <v>4</v>
@@ -29701,44 +30635,44 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B71">
         <f t="shared" ref="B71:B134" si="1">IF(A70=A71, B70+1, 1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D71" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F71" s="2">
         <f>IF(IF(RIGHT($A71,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A71,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B72">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D72" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F72" s="2">
         <f>IF(IF(RIGHT($A72,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A72,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -29747,18 +30681,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B73">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D73" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E73">
         <v>4</v>
@@ -29770,18 +30704,18 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B74">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E74">
         <v>4</v>
@@ -29793,18 +30727,18 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B75">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D75" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
       </c>
       <c r="E75">
         <v>4</v>
@@ -29816,18 +30750,18 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B76">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D76" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Scented Marker 10 Colors</v>
       </c>
       <c r="E76">
         <v>4</v>
@@ -29839,159 +30773,159 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B77">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D77" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2">
         <f>IF(IF(RIGHT($A77,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A77,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B78">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="D78" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v>Scented Sparkle Pen, 5Pck</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78" s="2">
         <f>IF(IF(RIGHT($A78,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A78,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B79">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D79" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
+        <v>Scented Swirl Pen, 5Pck</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" s="2">
         <f>IF(IF(RIGHT($A79,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A79,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B80">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D80" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+        <v>Scented Stacking Highlighters - 2-pack</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F80" s="2">
         <f>IF(IF(RIGHT($A80,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A80,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B81">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D81" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C81), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Sparkle Pen, 5Pck</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
       </c>
       <c r="E81">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F81" s="2">
         <f>IF(IF(RIGHT($A81,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A81,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B82">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D82" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C82), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Swirl Pen, 5Pck</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E82">
         <v>8</v>
       </c>
       <c r="F82" s="2">
         <f>IF(IF(RIGHT($A82,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C82), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C82), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A82,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C82), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C82), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B83">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D83" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C83), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Stacking Highlighters - 2-pack</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E83">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F83" s="2">
         <f>IF(IF(RIGHT($A83,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C83), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C83), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A83,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C83), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C83), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30000,44 +30934,44 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B84">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D84" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C84), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F84" s="2">
         <f>IF(IF(RIGHT($A84,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C84), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C84), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A84,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C84), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C84), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B85">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D85" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C85), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E85">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F85" s="2">
         <f>IF(IF(RIGHT($A85,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C85), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C85), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A85,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C85), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C85), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30046,18 +30980,18 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B86">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D86" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C86), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E86">
         <v>8</v>
@@ -30069,18 +31003,18 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B87">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D87" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C87, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C87), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E87">
         <v>8</v>
@@ -30092,21 +31026,21 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B88">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D88" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C88), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E88">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F88" s="2">
         <f>IF(IF(RIGHT($A88,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C88), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C88), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A88,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C88), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C88), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30115,18 +31049,18 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B89">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="D89" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C89, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C89), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E89">
         <v>8</v>
@@ -30138,21 +31072,21 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B90">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D90" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C90), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E90">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F90" s="2">
         <f>IF(IF(RIGHT($A90,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C90), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C90), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A90,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C90), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C90), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30161,18 +31095,18 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B91">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D91" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C91, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C91), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E91">
         <v>8</v>
@@ -30184,21 +31118,21 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B92">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D92" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C92), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E92">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="2">
         <f>IF(IF(RIGHT($A92,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C92), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C92), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A92,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C92), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C92), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30207,18 +31141,18 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B93">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D93" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C93, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C93), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E93">
         <v>4</v>
@@ -30230,18 +31164,18 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B94">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D94" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E94">
         <v>8</v>
@@ -30253,21 +31187,21 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B95">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D95" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C95), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E95">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F95" s="2">
         <f>IF(IF(RIGHT($A95,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C95), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C95), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A95,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C95), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C95), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30276,18 +31210,18 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B96">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D96" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E96">
         <v>4</v>
@@ -30299,21 +31233,21 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B97">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D97" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C97), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E97">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" s="2">
         <f>IF(IF(RIGHT($A97,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C97), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C97), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A97,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C97), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C97), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30322,18 +31256,18 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B98">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D98" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C98), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E98">
         <v>8</v>
@@ -30345,21 +31279,21 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B99">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D99" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E99">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F99" s="2">
         <f>IF(IF(RIGHT($A99,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C99), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C99), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A99,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C99), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C99), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30368,18 +31302,18 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B100">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D100" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C100, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C100), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E100">
         <v>4</v>
@@ -30391,21 +31325,21 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B101">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D101" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C101), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E101">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="2">
         <f>IF(IF(RIGHT($A101,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C101), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C101), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A101,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C101), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C101), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30414,21 +31348,21 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B102">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D102" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C102), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E102">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="2">
         <f>IF(IF(RIGHT($A102,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C102), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C102), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A102,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C102), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C102), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30437,18 +31371,18 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B103">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D103" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C103, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C103), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E103">
         <v>4</v>
@@ -30460,18 +31394,18 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B104">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D104" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C104, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C104), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E104">
         <v>4</v>
@@ -30483,113 +31417,113 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B105">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D105" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C105), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2">
         <f>IF(IF(RIGHT($A105,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C105), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C105), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A105,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C105), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C105), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B106">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="D106" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C106), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E106">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F106" s="2">
         <f>IF(IF(RIGHT($A106,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C106), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C106), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A106,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C106), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C106), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B107">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D107" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C107), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E107">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F107" s="2">
         <f>IF(IF(RIGHT($A107,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C107), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C107), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A107,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C107), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C107), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B108">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D108" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C108), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F108" s="2">
         <f>IF(IF(RIGHT($A108,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C108), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C108), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A108,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C108), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C108), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B109">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D109" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C109), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E109">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F109" s="2">
         <f>IF(IF(RIGHT($A109,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C109), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C109), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A109,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C109), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C109), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30598,18 +31532,18 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B110">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D110" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C110), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E110">
         <v>12</v>
@@ -30621,21 +31555,21 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B111">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D111" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C111), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E111">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F111" s="2">
         <f>IF(IF(RIGHT($A111,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C111), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C111), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A111,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C111), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C111), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30644,21 +31578,21 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B112">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D112" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C112), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E112">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F112" s="2">
         <f>IF(IF(RIGHT($A112,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C112), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C112), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A112,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C112), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C112), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30667,18 +31601,18 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B113">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D113" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E113">
         <v>12</v>
@@ -30690,21 +31624,21 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B114">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D114" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C114), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E114">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F114" s="2">
         <f>IF(IF(RIGHT($A114,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C114), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C114), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A114,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C114), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C114), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30713,21 +31647,21 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B115">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D115" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C115), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E115">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F115" s="2">
         <f>IF(IF(RIGHT($A115,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C115), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C115), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A115,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C115), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C115), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30736,21 +31670,21 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B116">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="D116" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C116), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
       </c>
       <c r="E116">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F116" s="2">
         <f>IF(IF(RIGHT($A116,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C116), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C116), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A116,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C116), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C116), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30759,18 +31693,18 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B117">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="D117" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E117">
         <v>12</v>
@@ -30782,21 +31716,21 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B118">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D118" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C118), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E118">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F118" s="2">
         <f>IF(IF(RIGHT($A118,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C118), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C118), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A118,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C118), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C118), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30805,21 +31739,21 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B119">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="D119" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C119), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E119">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F119" s="2">
         <f>IF(IF(RIGHT($A119,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C119), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C119), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A119,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C119), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C119), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30828,21 +31762,21 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B120">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D120" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C120), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E120">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F120" s="2">
         <f>IF(IF(RIGHT($A120,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C120), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C120), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A120,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C120), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C120), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30851,21 +31785,21 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B121">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="D121" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C121), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E121">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F121" s="2">
         <f>IF(IF(RIGHT($A121,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C121), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C121), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A121,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C121), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C121), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -30874,87 +31808,87 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B122">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D122" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C122), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E122">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F122" s="2">
         <f>IF(IF(RIGHT($A122,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C122), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C122), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A122,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C122), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C122), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B123">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D123" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C123), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E123">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F123" s="2">
         <f>IF(IF(RIGHT($A123,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C123), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C123), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A123,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C123), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C123), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B124">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D124" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C124), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E124">
         <v>8</v>
       </c>
       <c r="F124" s="2">
         <f>IF(IF(RIGHT($A124,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C124), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C124), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A124,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C124), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C124), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B125">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D125" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E125">
         <v>4</v>
@@ -30966,18 +31900,18 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B126">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D126" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C126, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C126), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
       </c>
       <c r="E126">
         <v>4</v>
@@ -30989,18 +31923,18 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B127">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D127" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C127, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C127), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E127">
         <v>8</v>
@@ -31012,18 +31946,18 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B128">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D128" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C128, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C128), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E128">
         <v>4</v>
@@ -31035,18 +31969,18 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B129">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="D129" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E129">
         <v>4</v>
@@ -31058,21 +31992,21 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B130">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D130" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C130), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E130">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130" s="2">
         <f>IF(IF(RIGHT($A130,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C130), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C130), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A130,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C130), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C130), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31081,18 +32015,18 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B131">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D131" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C131, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C131), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E131">
         <v>4</v>
@@ -31104,21 +32038,21 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B132">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D132" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C132), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E132">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F132" s="2">
         <f>IF(IF(RIGHT($A132,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C132), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C132), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A132,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C132), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C132), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31127,18 +32061,18 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B133">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D133" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C133, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C133), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E133">
         <v>4</v>
@@ -31150,18 +32084,18 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B134">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D134" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C134, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C134), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E134">
         <v>4</v>
@@ -31173,21 +32107,21 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B135">
-        <f t="shared" ref="B135:B176" si="2">IF(A134=A135, B134+1, 1)</f>
-        <v>6</v>
+        <f t="shared" ref="B135:B173" si="2">IF(A134=A135, B134+1, 1)</f>
+        <v>1</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D135" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C135), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
       </c>
       <c r="E135">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F135" s="2">
         <f>IF(IF(RIGHT($A135,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C135), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C135), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A135,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C135), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C135), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31196,18 +32130,18 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B136">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D136" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C136, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C136), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Snowed In</v>
       </c>
       <c r="E136">
         <v>4</v>
@@ -31219,21 +32153,21 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B137">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D137" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C137), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
       </c>
       <c r="E137">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F137" s="2">
         <f>IF(IF(RIGHT($A137,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C137), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C137), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A137,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C137), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C137), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31242,18 +32176,18 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B138">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D138" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C138, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C138), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+        <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
       </c>
       <c r="E138">
         <v>4</v>
@@ -31265,18 +32199,18 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B139">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="D139" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C139, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C139), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Snowed In</v>
+        <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
       </c>
       <c r="E139">
         <v>4</v>
@@ -31288,21 +32222,21 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B140">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D140" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C140), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E140">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F140" s="2">
         <f>IF(IF(RIGHT($A140,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C140), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C140), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A140,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C140), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C140), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31311,21 +32245,21 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B141">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D141" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C141), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F141" s="2">
         <f>IF(IF(RIGHT($A141,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C141), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C141), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A141,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C141), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C141), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31334,21 +32268,21 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B142">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D142" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C142), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F142" s="2">
         <f>IF(IF(RIGHT($A142,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C142), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C142), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A142,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C142), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C142), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31357,21 +32291,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B143">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D143" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C143), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E143">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F143" s="2">
         <f>IF(IF(RIGHT($A143,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C143), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C143), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A143,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C143), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C143), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31380,21 +32314,21 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B144">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D144" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C144), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
       </c>
       <c r="E144">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F144" s="2">
         <f>IF(IF(RIGHT($A144,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C144), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C144), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A144,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C144), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C144), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31403,94 +32337,94 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B145">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D145" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C145), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v xml:space="preserve">Universal Tabletop Display - Empty </v>
       </c>
       <c r="E145">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F145" s="2">
         <f>IF(IF(RIGHT($A145,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C145), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C145), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A145,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C145), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C145), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B146">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D146" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C146), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E146">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F146" s="2">
         <f>IF(IF(RIGHT($A146,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C146), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C146), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A146,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C146), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C146), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B147">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="D147" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C147), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E147">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F147" s="2">
         <f>IF(IF(RIGHT($A147,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C147), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C147), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A147,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C147), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C147), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B148">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="D148" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C148), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Universal Tabletop Display - Empty </v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F148" s="2">
         <f>IF(IF(RIGHT($A148,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C148), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C148), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A148,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C148), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C148), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -31499,17 +32433,17 @@
       </c>
       <c r="B149">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D149" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C149), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
+        <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E149">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F149" s="2">
         <f>IF(IF(RIGHT($A149,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C149), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C149), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A149,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C149), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C149), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31522,17 +32456,17 @@
       </c>
       <c r="B150">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D150" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C150), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E150">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F150" s="2">
         <f>IF(IF(RIGHT($A150,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C150), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C150), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A150,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C150), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C150), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31545,17 +32479,17 @@
       </c>
       <c r="B151">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D151" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C151), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
       <c r="E151">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F151" s="2">
         <f>IF(IF(RIGHT($A151,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C151), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C151), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A151,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C151), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C151), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31564,21 +32498,21 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B152">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D152" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C152), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E152">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F152" s="2">
         <f>IF(IF(RIGHT($A152,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C152), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C152), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A152,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C152), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C152), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31587,87 +32521,87 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B153">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D153" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C153), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E153">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F153" s="2">
         <f>IF(IF(RIGHT($A153,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C153), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C153), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A153,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C153), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C153), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B154">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D154" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C154), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E154">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F154" s="2">
         <f>IF(IF(RIGHT($A154,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C154), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C154), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A154,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C154), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C154), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B155">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="D155" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C155), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E155">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F155" s="2">
         <f>IF(IF(RIGHT($A155,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C155), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C155), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A155,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C155), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C155), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B156">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="D156" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C156, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C156), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E156">
         <v>4</v>
@@ -31679,18 +32613,18 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B157">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D157" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C157, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C157), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E157">
         <v>4</v>
@@ -31702,18 +32636,18 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B158">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D158" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C158, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C158), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E158">
         <v>4</v>
@@ -31725,18 +32659,18 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B159">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D159" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C159, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C159), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E159">
         <v>4</v>
@@ -31748,18 +32682,18 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B160">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D160" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C160, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C160), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E160">
         <v>4</v>
@@ -31771,41 +32705,41 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B161">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D161" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C161), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F161" s="2">
         <f>IF(IF(RIGHT($A161,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C161), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C161), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A161,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C161), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C161), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B162">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D162" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C162, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C162), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
       </c>
       <c r="E162">
         <v>4</v>
@@ -31817,90 +32751,90 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B163">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D163" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C163), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F163" s="2">
         <f>IF(IF(RIGHT($A163,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C163), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C163), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A163,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C163), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C163), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B164">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D164" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C164), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
       </c>
       <c r="E164">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F164" s="2">
         <f>IF(IF(RIGHT($A164,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C164), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C164), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A164,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C164), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C164), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B165">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="D165" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C165), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+        <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E165">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F165" s="2">
         <f>IF(IF(RIGHT($A165,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C165), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C165), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A165,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C165), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C165), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B166">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D166" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C166), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E166">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F166" s="2">
         <f>IF(IF(RIGHT($A166,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C166), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C166), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A166,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C166), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C166), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31909,18 +32843,18 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B167">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D167" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C167, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C167), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E167">
         <v>4</v>
@@ -31932,21 +32866,21 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B168">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D168" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C168), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E168">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F168" s="2">
         <f>IF(IF(RIGHT($A168,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C168), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C168), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A168,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C168), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C168), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -31955,41 +32889,41 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B169">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D169" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C169), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E169">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F169" s="2">
         <f>IF(IF(RIGHT($A169,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C169), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C169), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A169,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C169), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C169), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B170">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D170" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C170, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C170), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E170">
         <v>4</v>
@@ -32001,44 +32935,44 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B171">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D171" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E171">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F171" s="2">
         <f>IF(IF(RIGHT($A171,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C171), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C171), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A171,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C171), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C171), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B172">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D172" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C172), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E172">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F172" s="2">
         <f>IF(IF(RIGHT($A172,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C172), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C172), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A172,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C172), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C172), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
@@ -32047,93 +32981,24 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B173">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D173" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C173), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E173">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F173" s="2">
         <f>IF(IF(RIGHT($A173,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C173), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C173), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A173,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C173), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C173), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174" t="s">
-        <v>65</v>
-      </c>
-      <c r="B174">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D174" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C174), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
-      </c>
-      <c r="E174">
-        <v>1</v>
-      </c>
-      <c r="F174" s="2">
-        <f>IF(IF(RIGHT($A174,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C174), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C174), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A174,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C174), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C174), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175" t="s">
-        <v>65</v>
-      </c>
-      <c r="B175">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D175" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C175), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
-      </c>
-      <c r="E175">
-        <v>1</v>
-      </c>
-      <c r="F175" s="2">
-        <f>IF(IF(RIGHT($A175,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C175), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C175), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A175,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C175), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C175), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176" t="s">
-        <v>65</v>
-      </c>
-      <c r="B176">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D176" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C176), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E176">
-        <v>1</v>
-      </c>
-      <c r="F176" s="2">
-        <f>IF(IF(RIGHT($A176,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C176), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C176), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A176,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C176), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C176), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
@@ -32142,9 +33007,19 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:XFD176">
-    <cfRule type="expression" dxfId="6" priority="23">
+  <conditionalFormatting sqref="A5:XFD54 A57:XFD173">
+    <cfRule type="expression" dxfId="3" priority="25">
       <formula>IF($A5&lt;&gt;$A6, TRUE, FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56:XFD56">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>IF($A56&lt;&gt;#REF!, TRUE, FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55:XFD55">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>IF($A55&lt;&gt;$A56, TRUE, FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32152,26 +33027,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B10405EB6D76C04A99D739F71CB1C882" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="588855ac044783769b53e0cfeb370d1a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="856a7437-a7e7-4452-817c-46e435f59c4c" xmlns:ns3="0db41735-03c9-45f7-99e2-dcae27ef4500" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f4c0eefc11dc6e5e719c9a8931b7f89" ns2:_="" ns3:_="">
     <xsd:import namespace="856a7437-a7e7-4452-817c-46e435f59c4c"/>
@@ -32412,26 +33267,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
-    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32448,4 +33304,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
+    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{768BC053-FEAC-4327-9748-B4A035F50747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E475B03C-B55D-4F82-82F6-BC6CACE8EE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -284,7 +284,7 @@
     <t>LL-16-3246</t>
   </si>
   <si>
-    <t>LL-20-3293</t>
+    <t>LL-20-3297</t>
   </si>
 </sst>
 </file>
@@ -29784,7 +29784,7 @@
       </c>
       <c r="D6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C6, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C6), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Costal Calm</v>
+        <v>FlowArt: Mini Single - Postcard Places</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -30363,7 +30363,7 @@
       </c>
       <c r="D32" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C32), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Costal Calm</v>
+        <v>FlowArt: Mini Single - Postcard Places</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -30800,7 +30800,7 @@
       </c>
       <c r="D51" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Costal Calm</v>
+        <v>FlowArt: Mini Single - Postcard Places</v>
       </c>
       <c r="E51">
         <v>6</v>
@@ -33113,7 +33113,7 @@
       </c>
       <c r="D151" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C151), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Costal Calm</v>
+        <v>FlowArt: Mini Single - Postcard Places</v>
       </c>
       <c r="E151">
         <v>6</v>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="D156" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C156, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C156), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Costal Calm</v>
+        <v>FlowArt: Mini Single - Postcard Places</v>
       </c>
       <c r="E156">
         <v>6</v>
